--- a/resources/templates/standard/J1100-05.xlsx
+++ b/resources/templates/standard/J1100-05.xlsx
@@ -11,7 +11,10 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="38">
+  <si>
+    <t>{{companyLogo}}</t>
+  </si>
   <si>
     <t>제품 품질계획요약 및 완료확인서</t>
   </si>
@@ -732,12 +735,14 @@
   </cols>
   <sheetData>
     <row r="1" ht="20.15" customHeight="1" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A1" s="1"/>
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
       <c r="D1" s="1"/>
       <c r="E1" s="2" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F1" s="2"/>
       <c r="G1" s="2"/>
@@ -752,18 +757,18 @@
       <c r="P1" s="2"/>
       <c r="Q1" s="2"/>
       <c r="R1" s="3" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S1" s="4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T1" s="4"/>
       <c r="U1" s="4" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="V1" s="4"/>
       <c r="W1" s="4" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="X1" s="4"/>
     </row>
@@ -847,7 +852,7 @@
     </row>
     <row r="5" ht="24" customHeight="1" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A5" s="7" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B5" s="7"/>
       <c r="C5" s="7"/>
@@ -861,7 +866,7 @@
       <c r="K5" s="8"/>
       <c r="L5" s="8"/>
       <c r="M5" s="4" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="N5" s="4"/>
       <c r="O5" s="4"/>
@@ -877,7 +882,7 @@
     </row>
     <row r="6" ht="24" customHeight="1" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A6" s="10" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B6" s="10"/>
       <c r="C6" s="10"/>
@@ -891,7 +896,7 @@
       <c r="K6" s="11"/>
       <c r="L6" s="11"/>
       <c r="M6" s="12" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="N6" s="12"/>
       <c r="O6" s="12"/>
@@ -907,7 +912,7 @@
     </row>
     <row r="7" ht="24" customHeight="1" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A7" s="10" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B7" s="10"/>
       <c r="C7" s="10"/>
@@ -921,7 +926,7 @@
       <c r="K7" s="11"/>
       <c r="L7" s="11"/>
       <c r="M7" s="12" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="N7" s="12"/>
       <c r="O7" s="12"/>
@@ -937,13 +942,13 @@
     </row>
     <row r="8" ht="24" customHeight="1" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A8" s="13" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B8" s="13"/>
       <c r="C8" s="13"/>
       <c r="D8" s="13"/>
       <c r="E8" s="12" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F8" s="12"/>
       <c r="G8" s="12"/>
@@ -951,20 +956,20 @@
       <c r="I8" s="12"/>
       <c r="J8" s="12"/>
       <c r="K8" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="L8" s="12" t="s">
         <v>13</v>
-      </c>
-      <c r="L8" s="12" t="s">
-        <v>12</v>
       </c>
       <c r="M8" s="12"/>
       <c r="N8" s="12"/>
       <c r="O8" s="12"/>
       <c r="P8" s="12"/>
       <c r="Q8" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="R8" s="12" t="s">
         <v>13</v>
-      </c>
-      <c r="R8" s="12" t="s">
-        <v>12</v>
       </c>
       <c r="S8" s="12"/>
       <c r="T8" s="12"/>
@@ -972,7 +977,7 @@
       <c r="V8" s="12"/>
       <c r="W8" s="12"/>
       <c r="X8" s="14" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="9" ht="24" customHeight="1" spans="1:24" x14ac:dyDescent="0.25">
@@ -1029,45 +1034,45 @@
     </row>
     <row r="11" ht="24" customHeight="1" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A11" s="13" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B11" s="13"/>
       <c r="C11" s="13"/>
       <c r="D11" s="13"/>
       <c r="E11" s="12" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F11" s="12"/>
       <c r="G11" s="12"/>
       <c r="H11" s="12" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I11" s="12"/>
       <c r="J11" s="12" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K11" s="12"/>
       <c r="L11" s="12"/>
       <c r="M11" s="12" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="N11" s="12"/>
       <c r="O11" s="12" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="P11" s="12"/>
       <c r="Q11" s="12"/>
       <c r="R11" s="12" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="S11" s="12"/>
       <c r="T11" s="12" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="U11" s="12"/>
       <c r="V11" s="12"/>
       <c r="W11" s="12" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="X11" s="12"/>
     </row>
@@ -1203,7 +1208,7 @@
     </row>
     <row r="17" ht="24" customHeight="1" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A17" s="21" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B17" s="22"/>
       <c r="C17" s="22"/>
@@ -1231,10 +1236,10 @@
     </row>
     <row r="18" ht="24" customHeight="1" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A18" s="24" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B18" s="25" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C18" s="25"/>
       <c r="D18" s="25"/>
@@ -1246,7 +1251,7 @@
       <c r="J18" s="25"/>
       <c r="K18" s="25"/>
       <c r="L18" s="25" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="M18" s="25"/>
       <c r="N18" s="25"/>
@@ -1256,7 +1261,7 @@
       <c r="R18" s="25"/>
       <c r="S18" s="25"/>
       <c r="T18" s="4" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="U18" s="4"/>
       <c r="V18" s="4"/>
@@ -1268,7 +1273,7 @@
         <v>1</v>
       </c>
       <c r="B19" s="11" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C19" s="11"/>
       <c r="D19" s="11"/>
@@ -1280,7 +1285,7 @@
       <c r="J19" s="11"/>
       <c r="K19" s="11"/>
       <c r="L19" s="11" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="M19" s="11"/>
       <c r="N19" s="11"/>
@@ -1300,7 +1305,7 @@
         <v>2</v>
       </c>
       <c r="B20" s="11" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C20" s="11"/>
       <c r="D20" s="11"/>
@@ -1312,7 +1317,7 @@
       <c r="J20" s="11"/>
       <c r="K20" s="11"/>
       <c r="L20" s="11" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="M20" s="11"/>
       <c r="N20" s="11"/>
@@ -1332,7 +1337,7 @@
         <v>3</v>
       </c>
       <c r="B21" s="11" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C21" s="11"/>
       <c r="D21" s="11"/>
@@ -1344,7 +1349,7 @@
       <c r="J21" s="11"/>
       <c r="K21" s="11"/>
       <c r="L21" s="11" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="M21" s="11"/>
       <c r="N21" s="11"/>
@@ -1364,7 +1369,7 @@
         <v>4</v>
       </c>
       <c r="B22" s="11" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C22" s="11"/>
       <c r="D22" s="11"/>
@@ -1376,7 +1381,7 @@
       <c r="J22" s="11"/>
       <c r="K22" s="11"/>
       <c r="L22" s="11" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="M22" s="11"/>
       <c r="N22" s="11"/>
@@ -1396,7 +1401,7 @@
         <v>5</v>
       </c>
       <c r="B23" s="11" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C23" s="11"/>
       <c r="D23" s="11"/>
@@ -1408,7 +1413,7 @@
       <c r="J23" s="11"/>
       <c r="K23" s="11"/>
       <c r="L23" s="11" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="M23" s="11"/>
       <c r="N23" s="11"/>
@@ -1428,7 +1433,7 @@
         <v>6</v>
       </c>
       <c r="B24" s="11" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C24" s="11"/>
       <c r="D24" s="11"/>
@@ -1440,7 +1445,7 @@
       <c r="J24" s="11"/>
       <c r="K24" s="11"/>
       <c r="L24" s="11" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="M24" s="11"/>
       <c r="N24" s="11"/>
@@ -1460,7 +1465,7 @@
         <v>7</v>
       </c>
       <c r="B25" s="11" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C25" s="11"/>
       <c r="D25" s="11"/>
@@ -1472,7 +1477,7 @@
       <c r="J25" s="11"/>
       <c r="K25" s="11"/>
       <c r="L25" s="11" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="M25" s="11"/>
       <c r="N25" s="11"/>
@@ -1492,7 +1497,7 @@
         <v>8</v>
       </c>
       <c r="B26" s="11" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C26" s="11"/>
       <c r="D26" s="11"/>
@@ -1504,7 +1509,7 @@
       <c r="J26" s="11"/>
       <c r="K26" s="11"/>
       <c r="L26" s="11" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="M26" s="11"/>
       <c r="N26" s="11"/>
@@ -1524,7 +1529,7 @@
         <v>9</v>
       </c>
       <c r="B27" s="11" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C27" s="11"/>
       <c r="D27" s="11"/>
@@ -1536,7 +1541,7 @@
       <c r="J27" s="11"/>
       <c r="K27" s="11"/>
       <c r="L27" s="11" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="M27" s="11"/>
       <c r="N27" s="11"/>
